--- a/assets/Design/01 编码定义 (Codes).xlsx
+++ b/assets/Design/01 编码定义 (Codes).xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
   <si>
     <t>序号
 Index</t>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>文件或路径 “{0}” 不存在，请关注。</t>
+  </si>
+  <si>
+    <t>错误类型的参数 “{0}”。</t>
   </si>
 </sst>
 </file>
@@ -1325,18 +1328,18 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="str">
-        <f t="shared" ref="C2:C17" si="0">_xlfn.SWITCH(B2,"Trace","T","Debug","D","Information","I","Warning","W","Error","E","Exception","X")</f>
+        <f t="shared" ref="C2:C18" si="0">_xlfn.SWITCH(B2,"Trace","T","Debug","D","Information","I","Warning","W","Error","E","Exception","X")</f>
         <v>X</v>
       </c>
       <c r="D2" s="3" t="str">
-        <f t="shared" ref="D2:D17" si="1">"PL"&amp;C2&amp;RIGHT("0000"&amp;A2,4)</f>
+        <f t="shared" ref="D2:D18" si="1">"PL"&amp;C2&amp;RIGHT("0000"&amp;A2,4)</f>
         <v>PLX0001</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="4" t="str">
-        <f t="shared" ref="F2:F17" si="2">D2&amp;": "&amp;E2</f>
+        <f t="shared" ref="F2:F18" si="2">D2&amp;": "&amp;E2</f>
         <v>PLX0001: 应用程序抛出了一个未处理的异常。</v>
       </c>
     </row>
@@ -1693,24 +1696,42 @@
         <v>25</v>
       </c>
       <c r="C18" s="3" t="str">
-        <f>_xlfn.SWITCH(B18,"Trace","T","Debug","D","Information","I","Warning","W","Error","E","Exception","X")</f>
+        <f t="shared" si="0"/>
         <v>W</v>
       </c>
       <c r="D18" s="3" t="str">
-        <f>"PL"&amp;C18&amp;RIGHT("0000"&amp;A18,4)</f>
+        <f t="shared" si="1"/>
         <v>PLW0017</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="4" t="str">
-        <f>D18&amp;": "&amp;E18</f>
+        <f t="shared" si="2"/>
         <v>PLW0017: 文件或路径 “{0}” 不存在，请关注。</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:1">
+    <row r="19" customHeight="1" spans="1:6">
       <c r="A19" s="2">
         <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="3" t="str">
+        <f>_xlfn.SWITCH(B19,"Trace","T","Debug","D","Information","I","Warning","W","Error","E","Exception","X")</f>
+        <v>X</v>
+      </c>
+      <c r="D19" s="3" t="str">
+        <f>"PL"&amp;C19&amp;RIGHT("0000"&amp;A19,4)</f>
+        <v>PLX0018</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="4" t="str">
+        <f>D19&amp;": "&amp;E19</f>
+        <v>PLX0018: 错误类型的参数 “{0}”。</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:1">
@@ -1720,7 +1741,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B16 B17:B18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B17 B18:B19">
       <formula1>"Trace,Debug,Information,Warning,Error,Exception"</formula1>
     </dataValidation>
   </dataValidations>
